--- a/r5-aist-trustworthyai-main/ValueSet-trust-ai-human-oversight-action-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-trust-ai-human-oversight-action-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:13:25+00:00</t>
+    <t>2026-10-02T06:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
